--- a/wcag_scanner_implementation_matrix.xlsx
+++ b/wcag_scanner_implementation_matrix.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,44 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001D6A2D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007B5800"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00842029"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -71,8 +107,38 @@
         <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F8FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -86,11 +152,25 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -106,6 +186,30 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -472,67 +576,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>WCAG Guideline</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Implementation Status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Techniques Used</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Logic for Tags</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Logic Implementation</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>WCAG 2.1 Scanner Implementation Matrix | Last Updated: 2026-06-26 | Scanner: Go + axe-core v4.12 (Puppeteer/Node.js) | Status key: Implemented = fully covered in WCAGMap | Partial = limited/heuristic | Not Implemented = no WCAGMap entry</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.1.1 Non-text Content (A)</t>
+          <t>WCAG Guideline</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Implementation Status</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>H2, H24, H35, H36, H37, H53, H58, G94, F65</t>
+          <t>Techniques Used</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>img, input[type=image], object, svg, [role=img], area</t>
+          <t>Logic for Tags</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>image-alt: if &lt;img&gt; has no alt attr AND no aria-label/aria-labelledby AND no title, flag violation unless role=none/presentation. input-image-alt: &lt;input type=image&gt; must have alt. object-alt: &lt;object&gt; must have aria-label/aria-labelledby/title or body text. role-img-alt: [role=img] must have aria-label/aria-labelledby/title. svg-img-alt: &lt;svg&gt; with role img/graphics-document/graphics-symbol must have accessible name via aria-label/aria-labelledby/title/desc.</t>
+          <t>Logic Implementation</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.1.1 Non-text Content (A) - ARIA widgets</t>
+          <t>1.1.1 Non-text Content (A)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -542,537 +626,562 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARIA6, ARIA7</t>
+          <t>H2, H24, H35, H36, H37, H53, H58, G94, F65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[role=meter], [role=progressbar]</t>
+          <t>img, input[type=image], object, svg, [role=img], area</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>aria-meter-name: elements with role=meter must have accessible name via aria-label/aria-labelledby/title. aria-progressbar-name: elements with role=progressbar must have accessible name via aria-label/aria-labelledby/title.</t>
+          <t>image-alt: if &lt;img&gt; has no alt attr AND no aria-label/aria-labelledby AND no title, flag violation unless role=none/presentation. input-image-alt: &lt;input type=image&gt; must have alt. object-alt: &lt;object&gt; must have aria-label/aria-labelledby/title or body text. role-img-alt: [role=img] must have aria-label/aria-labelledby/title. svg-img-alt: &lt;svg&gt; with role img/graphics-document/graphics-symbol must have accessible name via aria-label/aria-labelledby/title/desc.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.2.1 Audio-only and Video-only (Prerecorded) (A)</t>
+          <t>1.1.1 Non-text Content (A) - ARIA widgets</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G158, G159, G166, H96</t>
+          <t>ARIA6, ARIA7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>audio, video</t>
+          <t>[role=meter], [role=progressbar]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AXE does not directly check for transcript presence for 1.2.1. Custom check needed: verify audio/video has adjacent transcript link or track[kind=captions/descriptions].</t>
+          <t>aria-meter-name: elements with role=meter must have accessible name via aria-label/aria-labelledby/title. aria-progressbar-name: elements with role=progressbar must have accessible name via aria-label/aria-labelledby/title.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.2.2 Captions (Prerecorded) (A)</t>
+          <t>1.2.1 Audio-only and Video-only (Prerecorded) (A)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>G87, G93, H96</t>
+          <t>G158, G159, G166, H96</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>video</t>
+          <t>audio, video</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AXE: video-caption checks &lt;video&gt; element has at least one &lt;track&gt; child with kind=captions or kind=subtitles. If no track element or track lacks src with .vtt extension, flag violation.</t>
+          <t>AXE does not directly check for transcript presence for 1.2.1. Custom check needed: verify audio/video has adjacent transcript link or track[kind=captions/descriptions].</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1.2.3 Audio Description or Media Alternative (Prerecorded) (A)</t>
+          <t>1.2.2 Captions (Prerecorded) (A)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>G58, G69, H53, G78, G173, G203, H96</t>
+          <t>G87, G93, H96</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>video, audio, object, iframe, embed</t>
+          <t>video</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Custom G58: For each media element (video, audio, object with multimedia, iframe with youtube/vimeo, embed with video), check adjacent siblings (±2) or figcaption for &lt;a&gt; with text containing 'transcript/alt/description' OR href ending .txt/.html. Custom H53: For &lt;object&gt; with multimedia data/type, clone node, remove &lt;param&gt;/&lt;embed&gt;, check body text &gt;30 chars OR contains &lt;a&gt; with transcript text OR body &gt;200 chars with dialogue format.</t>
+          <t>AXE: video-caption checks &lt;video&gt; element has at least one &lt;track&gt; child with kind=captions or kind=subtitles. If no track element or track lacks src with .vtt extension, flag violation.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.3.1 Info and Relationships (A)</t>
+          <t>1.2.3 Audio Description or Media Alternative (Prerecorded) (A)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>H42, H43, H44, H48, H63, H65, H71, H85, ARIA1, ARIA2, ARIA11, ARIA13, G115, G117</t>
+          <t>G58, G69, H53, G78, G173, G203, H96</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dl, dt, dd, li, ul, ol, table, th, td, h1-h6, p, figure, label, fieldset, legend</t>
+          <t>video, audio, object, iframe, embed</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>definition-list: &lt;dl&gt; must contain only &lt;dt&gt;, &lt;dd&gt;, or div wrappers. dlitem: &lt;dt&gt;/&lt;dd&gt; must be direct children of &lt;dl&gt;. list: &lt;ul&gt;/&lt;ol&gt; must have &lt;li&gt; children. listitem: &lt;li&gt; must be in &lt;ul&gt;/&lt;ol&gt;/&lt;menu&gt;. p-as-heading: &lt;p&gt; styled with bold/italic/font-size to look like heading must use actual heading tag. table-fake-caption: tables with caption must use &lt;caption&gt; not just text node. td-has-header: data cells in tables &gt;3x3 must have table headers. td-headers-attr: headers attr must reference valid th IDs. th-has-data-cells: &lt;th&gt; must describe at least one data cell. aria-required-children: ARIA roles requiring children must have them. aria-required-parent: ARIA roles requiring parent must be inside them.</t>
+          <t>Custom G58: For each media element (video, audio, object with multimedia, iframe with youtube/vimeo, embed with video), check adjacent siblings (±2) or figcaption for &lt;a&gt; with text containing 'transcript/alt/description' OR href ending .txt/.html. Custom H53: For &lt;object&gt; with multimedia data/type, clone node, remove &lt;param&gt;/&lt;embed&gt;, check body text &gt;30 chars OR contains &lt;a&gt; with transcript text OR body &gt;200 chars with dialogue format.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>1.3.1 Info and Relationships (A)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>H42, H43, H44, H48, H63, H65, H71, H85, ARIA1, ARIA2, ARIA11, ARIA13, G115, G117</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dl, dt, dd, li, ul, ol, table, th, td, h1-h6, p, figure, label, fieldset, legend</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>definition-list: &lt;dl&gt; must contain only &lt;dt&gt;, &lt;dd&gt;, or div wrappers. dlitem: &lt;dt&gt;/&lt;dd&gt; must be direct children of &lt;dl&gt;. list: &lt;ul&gt;/&lt;ol&gt; must have &lt;li&gt; children. listitem: &lt;li&gt; must be in &lt;ul&gt;/&lt;ol&gt;/&lt;menu&gt;. p-as-heading: &lt;p&gt; styled with bold/italic/font-size to look like heading must use actual heading tag. table-fake-caption: tables with caption must use &lt;caption&gt; not just text node. td-has-header: data cells in tables &gt;3x3 must have table headers. td-headers-attr: headers attr must reference valid th IDs. th-has-data-cells: &lt;th&gt; must describe at least one data cell. aria-required-children: ARIA roles requiring children must have them. aria-required-parent: ARIA roles requiring parent must be inside them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>1.3.1 Info and Relationships (A) - aria-hidden body</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>ARIA5, F15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>body</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>aria-hidden-body: document &lt;body&gt; must NOT have aria-hidden=true. If present, entire page is invisible to assistive tech.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>1.3.4 Orientation (AA)</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>G214, C33, C38</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>html, body, meta[name=viewport]</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>css-orientation-lock: detect CSS that locks orientation (e.g., @media (orientation) with display:none on one orientation). Checks for CSS transforms that prevent orientation changes or viewport settings that restrict rotation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>G214, C33</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>document.styleSheets (@media orientation rules), inline &lt;script&gt;</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>orientation-lock (custom check, Phase 3): Two detection paths:
+1. CSS scan — iterates document.styleSheets; finds @media (orientation: landscape|portrait) rules containing display:none or visibility:hidden → serious violation.
+2. JS scan — searches text content of inline &lt;script&gt; elements for screen.orientation.lock() API calls → incomplete (cannot confirm programmatic lock).
+Returns pass when neither pattern found.
+Rule ID 'orientation-lock' → SC 1.3.4 in wcag_mapping.go.
+GAP: Does not detect orientation lock in external JS files or framework event listeners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1.3.5 Identify Input Purpose (AA)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>H98, G218</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>input, select, textarea</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>autocomplete-valid: if autocomplete attribute is present on input/select/textarea, verify its value is in the HTML spec valid autocomplete token list (e.g., name, email, tel, address-line1). Flags invalid tokens like 'foo' or 'username'.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>1.4.1 Use of Color (A)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>G14, G182, G183, G205, F13, F73, F81</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>a, link</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>link-in-text-block: if &lt;a&gt; is inside a text block and color is the only distinguishing feature, check that the link has additional visual differentiation (underline, bold, border) OR sufficient color difference. Computes computedStyle color of link vs surrounding text and checks for non-color cues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>G14, G182, G183 (partial)</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>document.styleSheets (:focus, :invalid pseudo-class rules)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>color-only-indicator (custom check, heuristic): Scans CSS stylesheet rules matching :focus or :invalid pseudo-classes for background-color/border-color changes. For matched elements, checks for non-colour indicator — icon (svg/img/[role=img]) or text content. Flags serious violation if colour-only state change is detected.
+Rule ID 'color-only-indicator' → SC 1.4.1 in wcag_mapping.go.
+GAP: Does NOT implement link-in-text-block check (link-in-text-block rule is NOT in WCAGMap). Only covers :focus/:invalid CSS heuristic. Does not detect colour-only conveyance in charts, link-vs-body-text distinction, or error state colour-only indicators outside CSS pseudo-classes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>1.4.2 Audio Control (A)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>G60, G170, G171, H96</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>audio, video, embed</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no-autoplay-audio: if &lt;audio&gt; or &lt;video&gt; or &lt;embed&gt; has autoplay attribute, check if audio plays for &gt;3 seconds without a stop/pause/mute control. Flags elements where autoplay is present and no visible control mechanism is present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED. The rule 'no-autoplay-audio' is not in wcag_mapping.go and does not exist as a mapped rule in axe-core v4.12 or as a custom check in axe_runner.js.
+autoplay detection on &lt;audio&gt;/&lt;video&gt;/&lt;embed&gt; elements without a visible pause/stop/mute control is not covered.
+GAP: Requires custom check: detect autoplay attribute on media elements; verify presence of adjacent or accessible stop/pause/volume control within 3-second play window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="90" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>1.4.3 Contrast (Minimum) (AA)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>G18, G148, G174, G145, F24, F83, G195</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>text nodes, img of text, buttons, links, form controls, headings</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>color-contrast: for each text node, compute foreground color and background color. If ratio &lt; 4.5:1 for normal text or &lt; 3:1 for large text (18pt+ or 14pt+ bold), flag violation. Ignores disabled elements, invisible text, text on gradient images, and text with text-shadow. Excludes decorative text.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>1.4.4 Resize Text (AA)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>G142, C28, C29, C30, F69, F80, F94</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>meta[name=viewport]</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>meta-viewport: checks &lt;meta name=viewport&gt; content attribute does NOT contain user-scalable=no OR maximum-scale &lt; 2.0. If present, text cannot be zoomed to 200%, violating 1.4.4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1.4.6 Contrast (Enhanced) (AAA)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>G17, G18, G174, F83, G145</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>text nodes, img of text, buttons, links, form controls, headings</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>color-contrast-enhanced: same algorithm as color-contrast but thresholds are 7:1 for normal text and 4.5:1 for large text. Only runs when WCAG AAA level is selected in scanner config.</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>meta[name=viewport], document.documentElement (fontSize), elements with overflow:hidden</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Two checks:
+1. meta-viewport (axe-core, mapped → 1.4.10 + 1.4.4): &lt;meta name=viewport&gt; must not contain user-scalable=no or maximum-scale &lt; 2.0.
+2. resize-text (custom Puppeteer): Puppeteer sets document.documentElement.style.fontSize='200%'; detects: (a) horizontal scrollbar — scrollWidth &gt; window.innerWidth → serious violation; (b) overflow:hidden clipping — queries elements with overflow:hidden where scrollWidth &gt; clientWidth → serious violation. Font-size restored in finally block to prevent side-effects on subsequent checks.
+Rule ID 'resize-text' → SC 1.4.4 in wcag_mapping.go.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>1.4.6 Contrast (Enhanced) (AAA)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>G17, G18, G174, F83, G145</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>text nodes, img of text, buttons, links, form controls, headings</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>color-contrast-enhanced: same algorithm as color-contrast but thresholds are 7:1 for normal text and 4.5:1 for large text. Only runs when WCAG AAA level is selected in scanner config.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>1.4.12 Text Spacing (AA)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>C36, C35, C38</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>any element with inline style</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>avoid-inline-spacing: detects inline style attributes that set line-height, letter-spacing, or word-spacing with !important, which would prevent user CSS from overriding text spacing. Specifically checks style attributes containing 'line-height', 'letter-spacing', 'word-spacing' with !important.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="90" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>2.1.1 Keyboard (A)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>G202, G90, H91, SCR20, SCR29, F42, F54, F55, F58</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>iframe, frame, div, area, a, object, embed</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>frame-focusable-content: &lt;iframe&gt; or &lt;frame&gt; with focusable content must not have tabindex=-1. server-side-image-map: &lt;img&gt; or &lt;object&gt; with ismap attribute and &lt;a&gt; with coords not allowed. scrollable-region-focusable: scrollable &lt;div&gt; or &lt;section&gt; must be focusable via keyboard (have tabindex or be natively focusable).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>G202, G90, H91, SCR20, SCR29, F42, F54, F55, F58 (partial)</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>nested interactive elements</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>nested-interactive (axe-core, mapped in wcag_mapping.go → 2.1.1): Flags interactive elements nested inside other interactive elements (e.g., &lt;button&gt; inside &lt;a&gt;).
+Additional axe-core rules that fire but are NOT in wcag_mapping.go (results not attributed to SC 2.1.1 in scanner guideline breakdown):
+• frame-focusable-content: &lt;iframe&gt;/&lt;frame&gt; with focusable content must not have tabindex=-1.
+• scrollable-region-focusable: scrollable containers must be in the tab order.
+• server-side-image-map: &lt;img ismap&gt; disallows keyboard navigation.
+GAP: Register above rule IDs in wcag_mapping.go → '2.1.1' to surface their violations in the WCAG guideline breakdown. No full custom-widget keyboard operability test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>2.1.3 Keyboard (No Exception) (AAA)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>G202, G90, H91, SCR20, SCR29, F42, F54</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>div, section, article, main, iframe, frame</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>scrollable-region-focusable: same check as 2.1.1 but enforced at AAA level. All scrollable containers must be keyboard accessible regardless of content.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED. SC 2.1.3 is not registered in wcag_mapping.go. The scrollable-region-focusable axe-core rule fires but is not attributed to 2.1.3. No dedicated AAA-level keyboard check exists in axe_runner.js.
+GAP: Add 'scrollable-region-focusable' → '2.1.3' to wcag_mapping.go to partially cover this criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>2.2.1 Timing Adjustable (A)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>G133, G180, G198, G198, SCR1, SCR16, F40, F41, F58, F61</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>meta-refresh: checks for &lt;meta http-equiv=refresh&gt; with content &gt; 0. If present and no mechanism to stop/pause/extend, flag violation. Allows content=0 (immediate redirect) as acceptable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>G133, G180, G198, SCR1, SCR16, F40, F41, F58, F61</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>&lt;meta http-equiv=refresh&gt;, inline &lt;script&gt; (setTimeout/setInterval)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>timing-adjustable (custom check): Two detection paths:
+1. &lt;meta http-equiv='refresh'&gt;: extracts content seconds value; if &lt; 72000s (20h) → serious violation.
+2. Inline scripts: regex extracts setTimeout/setInterval duration arguments; if 3000ms–72000000ms (3s–20h) → incomplete.
+Returns pass when no timing constructs found.
+Rule ID 'timing-adjustable' → SC 2.2.1 in wcag_mapping.go.
+GAP: External JS files not scanned; server-side session timeouts undetectable; UI countdown timers not checked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>2.2.2 Pause, Stop, Hide (A)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>G4, G11, G152, G186, G187, SCR22, F50, F52, F61</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>blink, marquee</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>blink: detects &lt;blink&gt; elements (deprecated, auto-moving/blinking). marquee: detects &lt;marquee&gt; elements (auto-scrolling). Both are auto-updating content without pause/stop controls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED in wcag_mapping.go. axe-core includes blink and marquee rules that fire for &lt;blink&gt; and &lt;marquee&gt; elements, but neither rule ID is registered in wcag_mapping.go → results are not attributed to SC 2.2.2 in the scanner's guideline breakdown.
+GAP: (1) Register 'blink' and 'marquee' → '2.2.2' in wcag_mapping.go. (2) Add custom check for CSS animations (animation-duration, transition) on non-decorative content without pause/stop mechanism.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>2.2.4 Interruptions (AAA)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>G75, G76, G110, SCR14</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>meta-refresh-no-exceptions: at AAA level, any &lt;meta http-equiv=refresh&gt; with content &gt; 0 is a violation regardless of redirect purpose, since users cannot postpone/interrupt the refresh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2.4.1 Bypass Blocks (A)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>G1, G123, G124, H69, H70, SCR28, F66</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>a, body, main, nav</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>bypass: checks for at least one skip link mechanism. Must have an &lt;a&gt; with href starting with # that targets a valid element (main, [role=main], [id] element). Or first focusable element before main content. Or heading structure that allows navigation.</t>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED. SC 2.2.4 is not registered in wcag_mapping.go. The timing-adjustable check covers SC 2.2.1 only. No separate AAA-level interruptions check.
+GAP: Add 'timing-adjustable' → '2.2.4' in wcag_mapping.go, or create a dedicated meta-refresh-no-exceptions check for the AAA criterion.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2.4.2 Page Titled (A)</t>
+          <t>2.4.1 Bypass Blocks (A)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1082,240 +1191,243 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>G88, H25, F25</t>
+          <t>G1, G123, G124, H69, H70, SCR28, F66</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>a, body, main, nav</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>document-title: checks &lt;title&gt; element exists in &lt;head&gt; and is non-empty (length &gt; 0, not just whitespace). Also verifies title is unique and descriptive (not just 'Untitled' or duplicate across pages).</t>
+          <t>bypass: checks for at least one skip link mechanism. Must have an &lt;a&gt; with href starting with # that targets a valid element (main, [role=main], [id] element). Or first focusable element before main content. Or heading structure that allows navigation.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>2.4.2 Page Titled (A)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>G88, H25, F25</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>document-title: checks &lt;title&gt; element exists in &lt;head&gt; and is non-empty (length &gt; 0, not just whitespace). Also verifies title is unique and descriptive (not just 'Untitled' or duplicate across pages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>2.4.4 Link Purpose (In Context) (A)</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>G53, G91, H30, H33, H77, H78, H79, H80, H81, C7, F63, F89</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>a, area, [role=link]</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>link-name: checks &lt;a&gt; and &lt;area&gt; and [role=link] have accessible name. Name must come from text content, aria-label, aria-labelledby, or title. area-alt: &lt;area&gt; inside image map must have alt. If link contains only image, image must have alt.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2.4.9 Link Purpose (Link Only) (AAA)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>G53, G91, H30, H33, C7, F63, F89</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>a, [role=link]</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>identical-links-same-purpose: if multiple links on the page have the same accessible name, they must serve a similar purpose (point to same resource or equivalent). Groups links by accessible name and checks href targets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED in wcag_mapping.go. The axe-core rule identical-links-same-purpose (needs-review category) may fire when enabled, but is not registered in wcag_mapping.go and results are not attributed to SC 2.4.9.
+GAP: Register 'identical-links-same-purpose' → '2.4.9' in wcag_mapping.go to surface this criterion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2.5.3 Label in Name (A)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>G208, G211, F96, ARIA8, ARIA9, ARIA14, ARIA16</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>button, a, input, select, textarea, [role=button], [role=link]</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>label-content-name-mismatch: for elements labeled through visible text, the visible text must be part of the accessible name. Compares accessible name (from aria-label/aria-labelledby) with visible text. If they differ and visible text is not substring of accessible name, flag violation.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>2.5.8 Target Size (Minimum) (AA) - WCAG 2.2</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>G219, C42, F107</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>button, a, input, [role=button], [role=link], [onclick]</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>target-size: checks clickable elements have minimum size 24x24 CSS pixels OR sufficient spacing (no other target within 24px circle). Excludes inline links in text blocks, native checkbox/radio, and elements in mandatory fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>3.1.1 Language of Page (A)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>H57, H58, F57, F58</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>html-has-lang: &lt;html&gt; element must have lang attribute. html-lang-valid: lang value must be valid BCP 47 language tag (e.g., 'en', 'en-US', 'fr'). html-xml-lang-mismatch: if both lang and xml:lang exist, they must match.</t>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED. SC 2.5.8 is a WCAG 2.2 criterion (not covered by the WCAG 2.1 scope). The rule 'target-size' is not in wcag_mapping.go and may not be available in axe-core v4.12.
+GAP: If WCAG 2.2 support is desired, upgrade axe-core and register 'target-size' → '2.5.8' in wcag_mapping.go.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>3.1.1 Language of Page (A)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>H57, H58, F57, F58</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>html-has-lang: &lt;html&gt; element must have lang attribute. html-lang-valid: lang value must be valid BCP 47 language tag (e.g., 'en', 'en-US', 'fr'). html-xml-lang-mismatch: if both lang and xml:lang exist, they must match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>3.1.2 Language of Parts (AA)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>H58, F58</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>any element with lang</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>valid-lang: any element with lang attribute must have valid BCP 47 language tag. Does not check that the language actually matches the content, only that the tag format is valid.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>3.2.5 Change on Request (AAA)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>G76, G110, F9, F22, F36, F37, F52, F60, F61</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>meta-refresh-no-exceptions: same as 2.2.4 but enforced as AAA. Any meta refresh without user control is a change of context not on request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3.3.2 Labels or Instructions (A)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>H44, H65, H71, ARIA1, ARIA9, ARIA14, ARIA16, G131, G162, F68, F86, F89</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>input, select, textarea, label, [aria-label], [aria-labelledby]</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>form-field-multiple-labels: a form field must not have multiple &lt;label&gt; elements pointing to it (via for attribute). label: every form element must have a label via &lt;label for&gt;, aria-label, aria-labelledby, title, or placeholder (with sufficient context).</t>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Not Implemented</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>NOT IMPLEMENTED. SC 3.2.5 is not registered in wcag_mapping.go. The on-focus-context-change custom check covers SC 3.2.1 (On Focus) only. No separate 3.2.5 check for user-requested context changes (form submission, select dropdowns, etc.).
+GAP: Add 'on-focus-context-change' → '3.2.5' in wcag_mapping.go, or create a dedicated check for context changes triggered by form control input events.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4.1.1 Parsing (A)</t>
+          <t>3.3.2 Labels or Instructions (A)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1325,24 +1437,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>H74, H75, H93, H94, F70, F77, F79</t>
+          <t>H44, H65, H71, ARIA1, ARIA9, ARIA14, ARIA16, G131, G162, F68, F86, F89</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>any element with id</t>
+          <t>input, select, textarea, label, [aria-label], [aria-labelledby]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>duplicate-id: all id attribute values must be unique across the document. duplicate-id-active: id values of active elements (links, buttons, form fields) must be unique. duplicate-id-aria: id values used in ARIA and labels must be unique.</t>
+          <t>form-field-multiple-labels: a form field must not have multiple &lt;label&gt; elements pointing to it (via for attribute). label: every form element must have a label via &lt;label for&gt;, aria-label, aria-labelledby, title, or placeholder (with sufficient context).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4.1.2 Name, Role, Value (A)</t>
+          <t>4.1.1 Parsing (A)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1352,24 +1464,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>H64, H88, H91, ARIA1, ARIA4, ARIA5, ARIA6, ARIA7, ARIA8, ARIA9, ARIA10, ARIA11, ARIA12, ARIA13, ARIA14, ARIA15, ARIA16, G10, G108, G135, F15, F20, F42, F59, F68, F79, F86, F89, F91</t>
+          <t>H74, H75, H93, H94, F70, F77, F79</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>button, input, select, textarea, a, iframe, frame, [role], [aria-*]</t>
+          <t>any element with id</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>aria-allowed-attr: element's role must support its ARIA attributes. aria-required-attr: ARIA roles must have required attributes. aria-valid-attr: all aria-* must be valid attributes. aria-valid-attr-value: ARIA values must match spec. aria-roles: role must be valid. aria-deprecated-role: no deprecated roles. aria-hidden-focus: aria-hidden elements must not be focusable or contain focusables. button-name: buttons must have accessible name. input-button-name: input[type=button/submit/reset] must have value. frame-title: iframe/frame must have title. frame-title-unique: multiple iframe/frame must have unique titles. link-name: links must have discernible text. select-name: select must have accessible name. summary-name: summary must have discernible text. nested-interactive: interactive controls must not be nested.</t>
+          <t>duplicate-id: all id attribute values must be unique across the document. duplicate-id-active: id values of active elements (links, buttons, form fields) must be unique. duplicate-id-aria: id values used in ARIA and labels must be unique.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Best Practice - Keyboard</t>
+          <t>4.1.2 Name, Role, Value (A)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1379,24 +1491,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>G202, G90, F42, F54, F55</t>
+          <t>H64, H88, H91, ARIA1, ARIA4, ARIA5, ARIA6, ARIA7, ARIA8, ARIA9, ARIA10, ARIA11, ARIA12, ARIA13, ARIA14, ARIA15, ARIA16, G10, G108, G135, F15, F20, F42, F59, F68, F79, F86, F89, F91</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>any element with tabindex</t>
+          <t>button, input, select, textarea, a, iframe, frame, [role], [aria-*]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>tabindex: no tabindex &gt; 0. Positive tabindex disrupts natural tab order and should be avoided.</t>
+          <t>aria-allowed-attr: element's role must support its ARIA attributes. aria-required-attr: ARIA roles must have required attributes. aria-valid-attr: all aria-* must be valid attributes. aria-valid-attr-value: ARIA values must match spec. aria-roles: role must be valid. aria-deprecated-role: no deprecated roles. aria-hidden-focus: aria-hidden elements must not be focusable or contain focusables. button-name: buttons must have accessible name. input-button-name: input[type=button/submit/reset] must have value. frame-title: iframe/frame must have title. frame-title-unique: multiple iframe/frame must have unique titles. link-name: links must have discernible text. select-name: select must have accessible name. summary-name: summary must have discernible text. nested-interactive: interactive controls must not be nested.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Best Practice - Headings</t>
+          <t>Best Practice - Keyboard</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1406,24 +1518,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>G130, G141, H42, H69, F43</t>
+          <t>G202, G90, F42, F54, F55</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>h1-h6</t>
+          <t>any element with tabindex</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>heading-order: heading levels must not skip (h1 -&gt; h3 without h2 is flagged). empty-heading: headings must have visible text. page-has-heading-one: page or at least one frame must contain h1.</t>
+          <t>tabindex: no tabindex &gt; 0. Positive tabindex disrupts natural tab order and should be avoided.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Best Practice - Landmarks</t>
+          <t>Best Practice - Headings</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1433,24 +1545,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARIA11, ARIA13, ARIA20, G141, H69</t>
+          <t>G130, G141, H42, H69, F43</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>header, nav, main, aside, footer, section, [role=banner], [role=navigation], [role=main], [role=complementary], [role=contentinfo]</t>
+          <t>h1-h6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>landmark-one-main: document must have at least one main landmark. landmark-no-duplicate-main: at most one main. landmark-no-duplicate-banner: at most one banner. landmark-no-duplicate-contentinfo: at most one contentinfo. landmark-main-is-top-level: main must be top-level. landmark-banner-is-top-level: banner must be top-level. landmark-complementary-is-top-level: complementary must be top-level. landmark-contentinfo-is-top-level: contentinfo must be top-level. landmark-unique: all landmarks must be unique. region: all content must be in landmarks.</t>
+          <t>heading-order: heading levels must not skip (h1 -&gt; h3 without h2 is flagged). empty-heading: headings must have visible text. page-has-heading-one: page or at least one frame must contain h1.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Best Practice - Skip Links</t>
+          <t>Best Practice - Landmarks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1460,24 +1572,24 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>G1, G123, G124, SCR28</t>
+          <t>ARIA11, ARIA13, ARIA20, G141, H69</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>a[href^='#']</t>
+          <t>header, nav, main, aside, footer, section, [role=banner], [role=navigation], [role=main], [role=complementary], [role=contentinfo]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>skip-link: all skip links (href starting with #) must target a focusable element. If target is not focusable or does not exist, the skip link fails.</t>
+          <t>landmark-one-main: document must have at least one main landmark. landmark-no-duplicate-main: at most one main. landmark-no-duplicate-banner: at most one banner. landmark-no-duplicate-contentinfo: at most one contentinfo. landmark-main-is-top-level: main must be top-level. landmark-banner-is-top-level: banner must be top-level. landmark-complementary-is-top-level: complementary must be top-level. landmark-contentinfo-is-top-level: contentinfo must be top-level. landmark-unique: all landmarks must be unique. region: all content must be in landmarks.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Best Practice - Images</t>
+          <t>Best Practice - Skip Links</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1487,24 +1599,24 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>G94, G95, F38, F39, F65</t>
+          <t>G1, G123, G124, SCR28</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>img</t>
+          <t>a[href^='#']</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>image-redundant-alt: image alt text should not be repeated as adjacent visible text. If img is inside a link and alt matches link text, flag as redundant.</t>
+          <t>skip-link: all skip links (href starting with #) must target a focusable element. If target is not focusable or does not exist, the skip link fails.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Best Practice - Frames</t>
+          <t>Best Practice - Images</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1514,24 +1626,24 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>H64, H70, G141</t>
+          <t>G94, G95, F38, F39, F65</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>iframe, frame</t>
+          <t>img</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>frame-tested: iframe/frame must be testable by axe-core (same-origin or with axe-core injected). If iframe is cross-origin and not configured, content inside cannot be tested.</t>
+          <t>image-redundant-alt: image alt text should not be repeated as adjacent visible text. If img is inside a link and alt matches link text, flag as redundant.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Best Practice - Tables</t>
+          <t>Best Practice - Frames</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1541,24 +1653,24 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>H43, H63, H73, G115, G117, F91</t>
+          <t>H64, H70, G141</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>table, th, td, caption</t>
+          <t>iframe, frame</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>scope-attr-valid: scope attribute on th must be valid value (row, col, rowgroup, colgroup). empty-table-header: th elements must have discernible text. table-duplicate-name: caption must not contain same text as summary attribute.</t>
+          <t>frame-tested: iframe/frame must be testable by axe-core (same-origin or with axe-core injected). If iframe is cross-origin and not configured, content inside cannot be tested.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Best Practice - Focus Order</t>
+          <t>Best Practice - Tables</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1568,24 +1680,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>G59, G90, H4, SCR26, SCR27, F44, F85</t>
+          <t>H43, H63, H73, G115, G117, F91</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>a, button, input, [tabindex]</t>
+          <t>table, th, td, caption</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>focus-order-semantics: elements in tab order (tabindex &gt;= 0) must have a role appropriate for interactive content. If a static element has tabindex but no interactive role, flag as focus trap.</t>
+          <t>scope-attr-valid: scope attribute on th must be valid value (row, col, rowgroup, colgroup). empty-table-header: th elements must have discernible text. table-duplicate-name: caption must not contain same text as summary attribute.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Best Practice - ARIA Roles</t>
+          <t>Best Practice - Focus Order</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1595,24 +1707,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARIA4, ARIA5, ARIA6, ARIA7, F15, F20, F68, F79, F86, F89, F91</t>
+          <t>G59, G90, H4, SCR26, SCR27, F44, F85</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[role]</t>
+          <t>a, button, input, [tabindex]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>aria-allowed-role: role must be appropriate for the element (e.g., button role on div is allowed, but article role on button is not). aria-dialog-name: dialog/alertdialog should have accessible name. aria-text: role=text only on elements with no focusable descendants. aria-treeitem-name: treeitem must have accessible name. aria-braille-equivalent: aria-braillelabel/aria-brailleroledescription must have non-braille equivalent. presentation-role-conflict: presentational roles must not have global ARIA or tabindex.</t>
+          <t>focus-order-semantics: elements in tab order (tabindex &gt;= 0) must have a role appropriate for interactive content. If a static element has tabindex but no interactive role, flag as focus trap.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Best Practice - Viewport</t>
+          <t>Best Practice - ARIA Roles</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1622,24 +1734,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>G142, C28, C29, C30, F69, F80, F94</t>
+          <t>ARIA4, ARIA5, ARIA6, ARIA7, F15, F20, F68, F79, F86, F89, F91</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>meta[name=viewport]</t>
+          <t>[role]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>meta-viewport-large: viewport must allow scaling to a significant amount (not locked to device-width with no zoom). Checks that maximum-scale is not unreasonably restrictive.</t>
+          <t>aria-allowed-role: role must be appropriate for the element (e.g., button role on div is allowed, but article role on button is not). aria-dialog-name: dialog/alertdialog should have accessible name. aria-text: role=text only on elements with no focusable descendants. aria-treeitem-name: treeitem must have accessible name. aria-braille-equivalent: aria-braillelabel/aria-brailleroledescription must have non-braille equivalent. presentation-role-conflict: presentational roles must not have global ARIA or tabindex.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Best Practice - Forms</t>
+          <t>Best Practice - Viewport</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1649,24 +1761,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>H44, H65, H71, H88, G131, G162, F68, F86, F89</t>
+          <t>G142, C28, C29, C30, F69, F80, F94</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>input, select, textarea, label, [aria-label], [aria-labelledby]</t>
+          <t>meta[name=viewport]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>label-title-only: form elements must have visible labels, not just hidden labels or title/aria-describedby. Hidden labels (display:none, visibility:hidden) are insufficient.</t>
+          <t>meta-viewport-large: viewport must allow scaling to a significant amount (not locked to device-width with no zoom). Checks that maximum-scale is not unreasonably restrictive.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Best Practice - Hidden Content</t>
+          <t>Best Practice - Forms</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1676,48 +1788,437 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>G179, G182, G183, F49, F75</t>
+          <t>H44, H65, H71, H88, G131, G162, F68, F86, F89</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>any element</t>
+          <t>input, select, textarea, label, [aria-label], [aria-labelledby]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>hidden-content: informs users about hidden content. This is an informational rule that flags content hidden via CSS (display:none, visibility:hidden, aria-hidden=true) so reviewers can verify it is not essential content that should be accessible.</t>
+          <t>label-title-only: form elements must have visible labels, not just hidden labels or title/aria-describedby. Hidden labels (display:none, visibility:hidden) are insufficient.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Best Practice - Hidden Content</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>G179, G182, G183, F49, F75</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>any element</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>hidden-content: informs users about hidden content. This is an informational rule that flags content hidden via CSS (display:none, visibility:hidden, aria-hidden=true) so reviewers can verify it is not essential content that should be accessible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="90" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>1.3.2 Meaningful Sequence (A)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Partial</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>C27, C8, H34, H56, C6, F1, F32, F49</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>body, * [tabindex], * [style*="order"], * [style*="position"], * [style*="grid"], text nodes</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>meaningful-sequence-tabindex: flag elements with tabindex &gt; 0. meaningful-sequence-css-order: flag flex/grid children with computed order != 0. meaningful-sequence-absolute: flag non-decorative elements with position: absolute/fixed that may visually reorder content (INCOMPLETE). meaningful-sequence-grid: flag elements with explicit grid-row/grid-column placement (INCOMPLETE). meaningful-sequence-letter-spacing: flag text nodes using blank-character spacing without CSS letter-spacing. H34, H56, C6 remain NOT implemented (require manual review).</t>
         </is>
       </c>
     </row>
+    <row r="48" ht="90" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>1.3.3 Sensory Characteristics (A)</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>G96 (partial, heuristic)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Text nodes (TreeWalker)</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>sensory-characteristics (custom check, Phase 3, heuristic, incomplete-only): TreeWalker scans all text nodes. Regex detects sensory adjective (red/blue/round/upper/lower/left/right/etc.) within 60 characters of a UI noun (button/icon/link/field/image/etc.). Reports as incomplete (never violation) to avoid false positives. Returns pass when no patterns found.
+Rule ID 'sensory-characteristics' → SC 1.3.3 in wcag_mapping.go.
+GAP: High false-positive risk; cannot verify correctness of sensory instruction (e.g., 'click the blue submit button'). Only detects potential occurrences, cannot confirm whether non-sensory alternative exists.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="90" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>1.4.11 Non-text Contrast (AA)</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>G174, G195 (partial)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>input, textarea, select, button, [role=checkbox/radio/slider/switch/spinbutton]</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>non-text-contrast (custom Phase 1 check): Queries UI component elements. Computes border-color vs background-color contrast ratio using WCAG relative luminance formula. Flags serious violation when ratio &lt; 3:1.
+Rule ID 'non-text-contrast' → SC 1.4.11 in wcag_mapping.go.
+GAP: Does not cover all UI components (custom dropdowns, icon-only buttons, toggle switches, chart elements, progress indicators). Transparent backgrounds are skipped. Focus indicator contrast not checked separately from border contrast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="90" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>1.4.13 Content on Hover or Focus (AA)</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>C15 (partial)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Elements with [title], [data-tooltip], [data-tip], [aria-describedby] (up to 20)</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>content-on-hover (custom Puppeteer check, Phase 3): Stamps data-hov-idx on up to 20 candidate elements ([title]/[data-tooltip]/[data-tip]/[aria-describedby]). For each: records DOM size, hovers via page.hover(), waits 300ms, re-measures DOM. If DOM grew &gt;50 chars, dispatches Escape keydown and re-measures. If DOM shrinks → pass, else → moderate violation.
+Rule ID 'content-on-hover' → SC 1.4.13 in wcag_mapping.go.
+GAP: Limited to 20 candidates and title/data-tooltip attribute patterns. Does not test hover content persistence after pointer moves away, or focus-triggered tooltips directly. Dynamic content changes outside DOM size heuristic may be missed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="90" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>2.1.2 No Keyboard Trap (A)</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>G21, H91 (partial)</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>body (Tab simulation), [role=dialog], dialog, [aria-modal=true]</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>focus-order-cycling (custom Puppeteer check): Two sub-checks:
+1. Tab cycle — page.focus('body') then 50 × page.keyboard.press('Tab'); tracks visited element HTML fingerprints; cycle detected if focus returns to first element. No cycle detected → serious violation.
+2. Modal escape — finds [role=dialog]/dialog/[aria-modal=true]; dispatches Escape KeyboardEvent; checks if focus is still inside dialog → serious violation.
+Rule ID 'focus-order-cycling' → SC 2.1.2 (and 2.4.3) in wcag_mapping.go.
+GAP: 50-Tab limit may not reach all focusable elements on large pages. Synthetic Escape event may not trigger real modal close handlers. No widget-level keyboard trap check (e.g., custom date-pickers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="90" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>2.4.3 Focus Order (A)</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>G59, H4, SCR26, SCR27 (partial)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>body (Tab simulation) — same as 2.1.2</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>Shares focus-order-cycling Puppeteer check with SC 2.1.2 (same rule, dual mapping). Tab-cycle detection identifies non-cycling or stuck focus sequences. Rule ID 'focus-order-cycling' → SC 2.1.2 and 2.4.3 in wcag_mapping.go.
+GAP: Does not verify that focus order is logically meaningful or matches the visual/reading order. Detects only non-cycling focus (stuck or looping incorrectly). Limited to 50 Tab presses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="90" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>2.4.5 Multiple Ways (AA)</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>G63, G64, G125, G126, G161, G185 (partial, heuristic)</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>input[type=search], [role=search], a[href*=sitemap], input[name*=search]</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>multiple-ways (custom check, Phase 3, incomplete-only): Checks for search input presence: input[type=search], [role=search], form[action*=search], input[name*=search], input[placeholder*=earch]. Checks for sitemap link: any &lt;a&gt; whose text/href contains 'sitemap'. Returns pass if either found; reports incomplete if neither found.
+Rule ID 'multiple-ways' → SC 2.4.5 in wcag_mapping.go.
+GAP: Single-page scan only; cannot confirm site-wide navigation alternatives. No table-of-contents, related-links, or breadcrumb detection. Incomplete-only (never violation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="90" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>2.4.6 Headings and Labels (AA)</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>G130, G131 (partial)</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>h1–h6, label, [aria-label], [aria-labelledby]</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>Two axe-core rules mapped in wcag_mapping.go → SC 2.4.6 (via Best Practice – Headings):
+• empty-heading → 2.4.6: h1–h6 must have visible text content.
+• page-has-heading-one → 2.4.6: page must contain at least one h1.
+NOTE: heading-order (Best Practice – Headings row) maps to SC 2.4.10, not 2.4.6.
+GAP: Does not verify that headings are descriptive. Does not check label quality (placeholder-only, truncated, or generic labels). No check for forms with multiple required fields lacking group labels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="90" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>2.4.7 Focus Visible (AA)</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>G149, G165, G195, C15, SCR31</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Focusable elements (up to 30, via Puppeteer)</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>focus-visible (custom Puppeteer check, Phase 2): Stamps data-fv-idx on up to 30 focusable elements. For each:
+1. Captures pre-focus computed styles: outline, outline-width, outline-offset, box-shadow, border, border-color.
+2. Calls page.focus() to programmatically focus the element.
+3. Captures post-focus computed styles.
+4. Flags serious violation when all of outline, box-shadow, and border are unchanged and outline equals 'none'.
+Attribute stamps cleaned up after check. Rule ID 'focus-visible' → SC 2.4.7 in wcag_mapping.go.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="90" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>2.4.10 Section Headings (AAA)</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>G141 (partial)</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>h1–h6</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>heading-order (axe-core rule, mapped in wcag_mapping.go → SC 2.4.10): Checks that heading levels do not skip (e.g., h1→h3 without h2 is flagged as a violation).
+GAP: Does not verify that page sections are organised under headings. Does not detect sections without any heading. Heading-order checks sequence consistency only, not structural completeness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>2.5.1 Pointer Gestures (A)</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>G215 (partial, heuristic)</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Inline &lt;script&gt; elements</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>pointer-gestures (custom check, Phase 3, heuristic, incomplete-only): Scans inline &lt;script&gt; content for multi-touch gesture patterns (gesturestart, gesturechange, touchstart with e.touches.length &gt; 1, pinch/rotate keywords). If multi-touch pattern found, checks for single-pointer fallback (click handler, touchstart with touches.length === 1, or button/control for same action). If no fallback found → incomplete.
+Rule ID 'pointer-gestures' → SC 2.5.1 in wcag_mapping.go.
+GAP: Only scans inline scripts; external JS files not checked. Cannot detect gesture libraries (Hammer.js, HammerJS, etc.). Incomplete-only (never violation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>3.2.1 On Focus (A)</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>G107 (partial)</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Focusable elements (up to 20, via Puppeteer)</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>on-focus-context-change (custom Puppeteer check, Phase 2): Stamps data-oc-idx on up to 20 focusable elements. For each:
+1. Records current URL and count of open dialogs.
+2. Calls page.focus() and waits 200ms.
+3. Flags serious violation if URL changed or new dialog appeared.
+Navigates back if URL changed. Attribute stamps cleaned up after check.
+Rule ID 'on-focus-context-change' → SC 3.2.1 in wcag_mapping.go.
+GAP: Limited to 20 elements; 200ms may miss slow animations/transitions; external navigation (window.open) not detected; context change detection limited to URL and dialog count heuristic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>3.3.1 Error Identification (A)</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>G83, G84, G85, ARIA18, ARIA19, ARIA21 (partial)</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>[aria-invalid=true], input/select/textarea[required]</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>error-identification (custom Phase 1 check): Two-pass check:
+1. aria-invalid='true' elements: verifies accessible error message via aria-describedby pointing to non-empty referenced element text, OR adjacent [role=alert]/[aria-live] with non-empty text. Flags serious violation if no accessible error message found; pass if present.
+2. Native required fields (input/select/textarea[required]) without aria-describedby or aria-errormessage → flagged as incomplete (may lack programmatic error description).
+Rule ID 'error-identification' → SC 3.3.1 in wcag_mapping.go.
+GAP: Does not detect errors surfaced only via HTML5 constraint validation UI (browser default popups). Does not check custom error indicator patterns without ARIA attributes.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1741,7 +2242,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TECHNIQUE COVERAGE SUMMARY | Total Unique Techniques: 185 | Implemented: 169 | Partial: 9 | Not Implemented: 7</t>
+          <t>WCAG SCANNER IMPLEMENTATION MATRIX | Last Updated: 2026-06-26 | Total SC/Categories: 57 | Implemented: 34 | Partial: 16 | Not Implemented: 7</t>
         </is>
       </c>
     </row>
